--- a/task192/golden/boletim_vigilancia_2026S2.xlsx
+++ b/task192/golden/boletim_vigilancia_2026S2.xlsx
@@ -28,52 +28,52 @@
     <t>Vigilancia Nacional: boletim do periodo de 1 de maio a 30 de outubro de 2026</t>
   </si>
   <si>
-    <t>Indicador 2 do protocolo. Registo extraido em 6 de novembro de 2026; o numero de acoes de confronto e o das acoes que o foram.</t>
+    <t>Indicador 2 do protocolo, ao mais proximo de cinquenta acoes. Registo extraido em 6 de novembro de 2026; o numero de acoes de confronto e o das acoes que o foram, nao o dos codigos atribuidos.</t>
   </si>
   <si>
     <t>Acoes de confronto do periodo</t>
   </si>
   <si>
-    <t>234 acoes</t>
+    <t>450 acoes</t>
   </si>
   <si>
     <t>Acoes registadas no periodo</t>
   </si>
   <si>
-    <t>4790 acoes</t>
+    <t>4627 acoes</t>
   </si>
   <si>
     <t>Acoes com relato do monitor de imprensa</t>
   </si>
   <si>
-    <t>4357 acoes</t>
+    <t>4200 acoes</t>
   </si>
   <si>
     <t>Acoes so com relato de parceiro ou da linha</t>
   </si>
   <si>
-    <t>433 acoes</t>
+    <t>427 acoes</t>
   </si>
   <si>
     <t>Codigo de confronto do classificador</t>
   </si>
   <si>
-    <t>153 acoes</t>
+    <t>302 acoes</t>
   </si>
   <si>
     <t>Codigo de confronto de quem entregou</t>
   </si>
   <si>
-    <t>25 acoes</t>
+    <t>30 acoes</t>
   </si>
   <si>
     <t>Relatos na amostra de dupla codificacao</t>
   </si>
   <si>
-    <t>2600 relatos</t>
-  </si>
-  <si>
-    <t>As acoes com relato do monitor de imprensa levam o codigo do classificador (protocolo 2.6), medido pela mesa de codificacao na amostra de dupla codificacao do periodo.</t>
+    <t>1000 relatos</t>
+  </si>
+  <si>
+    <t>As acoes com relato do monitor de imprensa levam o codigo do classificador (protocolo 2.6). As duas rondas de dupla codificacao do periodo fecharam em 20 de junho e em 10 de setembro de 2026 e cobrem os relatos de 1 de maio a 31 de agosto.</t>
   </si>
   <si>
     <t>Preparado para o conselho de curadores de 19 de novembro de 2026.</t>
@@ -217,7 +217,7 @@
     <t>2026-10-30</t>
   </si>
   <si>
-    <t>Uma acao e um tema numa localidade num dia, qualquer que seja o numero de relatos. A quota e a parte das acoes da quinzena que a rede de parceiros relatou.</t>
+    <t>Uma acao e um tema numa localidade num dia, qualquer que seja o numero de relatos. A quota e a parte das acoes da quinzena que a rede de parceiros relatou. As quinzenas tem catorze dias e a ultima tem quinze.</t>
   </si>
   <si>
     <t>Relatos por via de acesso no periodo</t>
@@ -325,7 +325,7 @@
     <t>Indicador 2</t>
   </si>
   <si>
-    <t>Acoes de confronto do protocolo 3.3, em numero inteiro de acoes.</t>
+    <t>Acoes de confronto do protocolo 3.3, ao mais proximo de cinquenta acoes.</t>
   </si>
   <si>
     <t>Acao</t>
@@ -343,7 +343,7 @@
     <t>Quinzenas</t>
   </si>
   <si>
-    <t>Contadas a partir de 1 de maio; a ultima tem quinze dias e termina com o periodo (protocolo 3.4).</t>
+    <t>Catorze dias cada, contadas a partir de 1 de maio; os dias que sobram entram na ultima, que tem quinze (protocolo 3.4).</t>
   </si>
   <si>
     <t>Carga de agosto</t>
@@ -355,13 +355,13 @@
     <t>Relogios</t>
   </si>
   <si>
-    <t>O carimbo de recepcao do monitor de imprensa vem em UTC; as horas de inicio das acoes sao locais.</t>
+    <t>O carimbo de recepcao do monitor de imprensa e o do portal de parceiros vem em UTC; a hora de inicio de cada acao vem no relogio local do seu distrito, e os Acores estao uma hora atras do continente.</t>
   </si>
   <si>
     <t>Dupla codificacao</t>
   </si>
   <si>
-    <t>Duas rondas, julho e novembro, sobre relatos aceites do monitor (protocolo 4.5).</t>
+    <t>Duas rondas, fechadas em 20 de junho e em 10 de setembro, sobre os relatos aceites do monitor entrados desde o fecho anterior (protocolo 4.5). A ronda de outono e do periodo seguinte.</t>
   </si>
 </sst>
 </file>
@@ -916,13 +916,13 @@
         <v>27</v>
       </c>
       <c r="D4" s="12">
-        <v>247</v>
+        <v>289</v>
       </c>
       <c r="E4" s="12">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="F4" s="13">
-        <v>22.7</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -936,13 +936,13 @@
         <v>30</v>
       </c>
       <c r="D5" s="12">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="E5" s="12">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="F5" s="13">
-        <v>23.8</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -956,13 +956,13 @@
         <v>33</v>
       </c>
       <c r="D6" s="12">
-        <v>261</v>
+        <v>234</v>
       </c>
       <c r="E6" s="12">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="F6" s="13">
-        <v>28.4</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -976,13 +976,13 @@
         <v>36</v>
       </c>
       <c r="D7" s="12">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="E7" s="12">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F7" s="13">
-        <v>25.4</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -996,13 +996,13 @@
         <v>39</v>
       </c>
       <c r="D8" s="12">
-        <v>237</v>
+        <v>265</v>
       </c>
       <c r="E8" s="12">
         <v>104</v>
       </c>
       <c r="F8" s="13">
-        <v>23.6</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1016,13 +1016,13 @@
         <v>42</v>
       </c>
       <c r="D9" s="12">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E9" s="12">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F9" s="13">
-        <v>29.3</v>
+        <v>23.6</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1036,13 +1036,13 @@
         <v>45</v>
       </c>
       <c r="D10" s="12">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="E10" s="12">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="F10" s="13">
-        <v>22.7</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1056,13 +1056,13 @@
         <v>48</v>
       </c>
       <c r="D11" s="12">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="E11" s="12">
         <v>105</v>
       </c>
       <c r="F11" s="13">
-        <v>25.1</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1076,13 +1076,13 @@
         <v>51</v>
       </c>
       <c r="D12" s="12">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="E12" s="12">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="F12" s="13">
-        <v>31.8</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1096,13 +1096,13 @@
         <v>54</v>
       </c>
       <c r="D13" s="12">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="E13" s="12">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F13" s="13">
-        <v>24.6</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1116,13 +1116,13 @@
         <v>57</v>
       </c>
       <c r="D14" s="12">
-        <v>648</v>
+        <v>565</v>
       </c>
       <c r="E14" s="12">
         <v>118</v>
       </c>
       <c r="F14" s="13">
-        <v>27.3</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1136,13 +1136,13 @@
         <v>60</v>
       </c>
       <c r="D15" s="12">
-        <v>623</v>
+        <v>554</v>
       </c>
       <c r="E15" s="12">
         <v>119</v>
       </c>
       <c r="F15" s="13">
-        <v>27.4</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1156,13 +1156,13 @@
         <v>63</v>
       </c>
       <c r="D16" s="12">
-        <v>683</v>
+        <v>657</v>
       </c>
       <c r="E16" s="12">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F16" s="13">
-        <v>25</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
@@ -1210,13 +1210,13 @@
         <v>70</v>
       </c>
       <c r="B4" s="12">
-        <v>4505</v>
+        <v>4346</v>
       </c>
       <c r="C4" s="12">
         <v>148</v>
       </c>
       <c r="D4" s="13">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1224,13 +1224,13 @@
         <v>71</v>
       </c>
       <c r="B5" s="12">
-        <v>1298</v>
+        <v>1204</v>
       </c>
       <c r="C5" s="12">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D5" s="13">
-        <v>656</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1238,13 +1238,13 @@
         <v>72</v>
       </c>
       <c r="B6" s="12">
-        <v>967</v>
+        <v>945</v>
       </c>
       <c r="C6" s="12">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D6" s="13">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1299,13 +1299,13 @@
         <v>81</v>
       </c>
       <c r="C4" s="12">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="D4" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" s="12">
-        <v>928</v>
+        <v>851</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -1316,13 +1316,13 @@
         <v>83</v>
       </c>
       <c r="C5" s="12">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D5" s="12">
         <v>2</v>
       </c>
       <c r="E5" s="12">
-        <v>2481</v>
+        <v>2493</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -1333,13 +1333,13 @@
         <v>85</v>
       </c>
       <c r="C6" s="12">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D6" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" s="12">
-        <v>1566</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -1350,13 +1350,13 @@
         <v>87</v>
       </c>
       <c r="C7" s="12">
-        <v>153</v>
+        <v>127</v>
       </c>
       <c r="D7" s="12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E7" s="12">
-        <v>907</v>
+        <v>742</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -1367,13 +1367,13 @@
         <v>89</v>
       </c>
       <c r="C8" s="12">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="D8" s="12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E8" s="12">
-        <v>621</v>
+        <v>559</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -1384,13 +1384,13 @@
         <v>91</v>
       </c>
       <c r="C9" s="12">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="D9" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="12">
-        <v>497</v>
+        <v>413</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -1401,13 +1401,13 @@
         <v>93</v>
       </c>
       <c r="C10" s="12">
-        <v>156</v>
+        <v>120</v>
       </c>
       <c r="D10" s="12">
         <v>1</v>
       </c>
       <c r="E10" s="12">
-        <v>992</v>
+        <v>732</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">

--- a/task192/golden/boletim_vigilancia_2026S2.xlsx
+++ b/task192/golden/boletim_vigilancia_2026S2.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="117">
   <si>
     <t>Vigilancia Nacional: boletim do periodo de 1 de maio a 30 de outubro de 2026</t>
   </si>
@@ -362,6 +362,18 @@
   </si>
   <si>
     <t>Duas rondas, fechadas em 20 de junho e em 10 de setembro, sobre os relatos aceites do monitor entrados desde o fecho anterior (protocolo 4.5). A ronda de outono e do periodo seguinte.</t>
+  </si>
+  <si>
+    <t>Temas</t>
+  </si>
+  <si>
+    <t>Dos catorze temas de disputa do protocolo (2.7), energia e redes e florestas e fogos entraram no registo com a mobilizacao de setembro.</t>
+  </si>
+  <si>
+    <t>Contador de importacao</t>
+  </si>
+  <si>
+    <t>O contador diario por via conta cada chegada, pelo que a carga reposta de agosto esta contada outra vez em 14 de setembro; cada relato conta uma vez.</t>
   </si>
 </sst>
 </file>
@@ -1427,7 +1439,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F18F0FDB-C854-54C9-B989-812EBD8BBDAB}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1503,6 +1515,22 @@
         <v>112</v>
       </c>
     </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>116</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/task192/golden/boletim_vigilancia_2026S2.xlsx
+++ b/task192/golden/boletim_vigilancia_2026S2.xlsx
@@ -97,7 +97,7 @@
     <t>Municipios tocados</t>
   </si>
   <si>
-    <t>Quota da rede de parceiros, %</t>
+    <t>Acoes relatadas pela rede de parceiros</t>
   </si>
   <si>
     <t>Q1</t>
@@ -217,7 +217,7 @@
     <t>2026-10-30</t>
   </si>
   <si>
-    <t>Uma acao e um tema numa localidade num dia, qualquer que seja o numero de relatos. A quota e a parte das acoes da quinzena que a rede de parceiros relatou. As quinzenas tem catorze dias e a ultima tem quinze.</t>
+    <t>Uma acao e um tema numa localidade num dia, qualquer que seja o numero de relatos. A ultima coluna conta as acoes da quinzena de que a rede de parceiros entregou relato, cada acao uma vez. As quinzenas tem catorze dias e a ultima tem quinze.</t>
   </si>
   <si>
     <t>Relatos por via de acesso no periodo</t>
@@ -889,7 +889,7 @@
     <col min="3" max="3" width="13.7109375" customWidth="1"/>
     <col min="4" max="4" width="17.7109375" customWidth="1"/>
     <col min="5" max="5" width="18.7109375" customWidth="1"/>
-    <col min="6" max="6" width="26.7109375" customWidth="1"/>
+    <col min="6" max="6" width="32.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -933,8 +933,8 @@
       <c r="E4" s="12">
         <v>111</v>
       </c>
-      <c r="F4" s="13">
-        <v>23.9</v>
+      <c r="F4" s="12">
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -953,8 +953,8 @@
       <c r="E5" s="12">
         <v>110</v>
       </c>
-      <c r="F5" s="13">
-        <v>26.5</v>
+      <c r="F5" s="12">
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -973,8 +973,8 @@
       <c r="E6" s="12">
         <v>100</v>
       </c>
-      <c r="F6" s="13">
-        <v>20.9</v>
+      <c r="F6" s="12">
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -993,8 +993,8 @@
       <c r="E7" s="12">
         <v>103</v>
       </c>
-      <c r="F7" s="13">
-        <v>20.2</v>
+      <c r="F7" s="12">
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1013,8 +1013,8 @@
       <c r="E8" s="12">
         <v>104</v>
       </c>
-      <c r="F8" s="13">
-        <v>25.3</v>
+      <c r="F8" s="12">
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1033,8 +1033,8 @@
       <c r="E9" s="12">
         <v>103</v>
       </c>
-      <c r="F9" s="13">
-        <v>23.6</v>
+      <c r="F9" s="12">
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1053,8 +1053,8 @@
       <c r="E10" s="12">
         <v>100</v>
       </c>
-      <c r="F10" s="13">
-        <v>27.8</v>
+      <c r="F10" s="12">
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1073,8 +1073,8 @@
       <c r="E11" s="12">
         <v>105</v>
       </c>
-      <c r="F11" s="13">
-        <v>25.5</v>
+      <c r="F11" s="12">
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1093,8 +1093,8 @@
       <c r="E12" s="12">
         <v>111</v>
       </c>
-      <c r="F12" s="13">
-        <v>23.4</v>
+      <c r="F12" s="12">
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1113,8 +1113,8 @@
       <c r="E13" s="12">
         <v>116</v>
       </c>
-      <c r="F13" s="13">
-        <v>24.8</v>
+      <c r="F13" s="12">
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1133,8 +1133,8 @@
       <c r="E14" s="12">
         <v>118</v>
       </c>
-      <c r="F14" s="13">
-        <v>26.5</v>
+      <c r="F14" s="12">
+        <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1153,8 +1153,8 @@
       <c r="E15" s="12">
         <v>119</v>
       </c>
-      <c r="F15" s="13">
-        <v>26.4</v>
+      <c r="F15" s="12">
+        <v>146</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1173,8 +1173,8 @@
       <c r="E16" s="12">
         <v>119</v>
       </c>
-      <c r="F16" s="13">
-        <v>25.4</v>
+      <c r="F16" s="12">
+        <v>167</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
@@ -1419,7 +1419,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="12">
-        <v>732</v>
+        <v>726</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">

--- a/task192/golden/boletim_vigilancia_2026S2.xlsx
+++ b/task192/golden/boletim_vigilancia_2026S2.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="119">
   <si>
     <t>Vigilancia Nacional: boletim do periodo de 1 de maio a 30 de outubro de 2026</t>
   </si>
@@ -40,37 +40,43 @@
     <t>Acoes registadas no periodo</t>
   </si>
   <si>
-    <t>4627 acoes</t>
+    <t>4656 acoes</t>
   </si>
   <si>
     <t>Acoes com relato do monitor de imprensa</t>
   </si>
   <si>
-    <t>4200 acoes</t>
+    <t>4228 acoes</t>
   </si>
   <si>
     <t>Acoes so com relato de parceiro ou da linha</t>
   </si>
   <si>
-    <t>427 acoes</t>
+    <t>428 acoes</t>
   </si>
   <si>
     <t>Codigo de confronto do classificador</t>
   </si>
   <si>
-    <t>302 acoes</t>
+    <t>271 acoes</t>
   </si>
   <si>
     <t>Codigo de confronto de quem entregou</t>
   </si>
   <si>
-    <t>30 acoes</t>
+    <t>49 acoes</t>
   </si>
   <si>
     <t>Relatos na amostra de dupla codificacao</t>
   </si>
   <si>
-    <t>1000 relatos</t>
+    <t>1064 relatos</t>
+  </si>
+  <si>
+    <t>Desses, com codificacao manual</t>
+  </si>
+  <si>
+    <t>1056 relatos</t>
   </si>
   <si>
     <t>As acoes com relato do monitor de imprensa levam o codigo do classificador (protocolo 2.6). As duas rondas de dupla codificacao do periodo fecharam em 20 de junho e em 10 de setembro de 2026 e cobrem os relatos de 1 de maio a 31 de agosto.</t>
@@ -361,7 +367,7 @@
     <t>Dupla codificacao</t>
   </si>
   <si>
-    <t>Duas rondas, fechadas em 20 de junho e em 10 de setembro, sobre os relatos aceites do monitor entrados desde o fecho anterior (protocolo 4.5). A ronda de outono e do periodo seguinte.</t>
+    <t>Duas rondas, fechadas em 20 de junho e em 10 de setembro, sobre os relatos aceites do monitor entrados desde o fecho anterior (protocolo 4.5). A ronda de outono e do periodo seguinte. Os relatos que a mesa nao conseguiu codificar ficam na folha sem codigo manual e nao comparam codigos.</t>
   </si>
   <si>
     <t>Temas</t>
@@ -791,7 +797,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29EEEE36-8E6D-5F67-A472-E45A1B91774C}">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.7109375" customWidth="1"/>
@@ -864,14 +870,22 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
         <v>16</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -894,204 +908,204 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D4" s="12">
-        <v>289</v>
+        <v>264</v>
       </c>
       <c r="E4" s="12">
-        <v>111</v>
+        <v>70</v>
       </c>
       <c r="F4" s="12">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D5" s="12">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="E5" s="12">
-        <v>110</v>
+        <v>63</v>
       </c>
       <c r="F5" s="12">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D6" s="12">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="E6" s="12">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="F6" s="12">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D7" s="12">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="E7" s="12">
-        <v>103</v>
+        <v>68</v>
       </c>
       <c r="F7" s="12">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D8" s="12">
-        <v>265</v>
+        <v>222</v>
       </c>
       <c r="E8" s="12">
-        <v>104</v>
+        <v>65</v>
       </c>
       <c r="F8" s="12">
-        <v>67</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D9" s="12">
-        <v>259</v>
+        <v>237</v>
       </c>
       <c r="E9" s="12">
-        <v>103</v>
+        <v>66</v>
       </c>
       <c r="F9" s="12">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D10" s="12">
-        <v>230</v>
+        <v>252</v>
       </c>
       <c r="E10" s="12">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="F10" s="12">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D11" s="12">
-        <v>231</v>
+        <v>260</v>
       </c>
       <c r="E11" s="12">
-        <v>105</v>
+        <v>66</v>
       </c>
       <c r="F11" s="12">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D12" s="12">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="E12" s="12">
-        <v>111</v>
+        <v>69</v>
       </c>
       <c r="F12" s="12">
         <v>58</v>
@@ -1099,87 +1113,87 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D13" s="12">
-        <v>581</v>
+        <v>639</v>
       </c>
       <c r="E13" s="12">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F13" s="12">
-        <v>144</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D14" s="12">
-        <v>565</v>
+        <v>589</v>
       </c>
       <c r="E14" s="12">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="F14" s="12">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D15" s="12">
-        <v>554</v>
+        <v>588</v>
       </c>
       <c r="E15" s="12">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="F15" s="12">
-        <v>146</v>
+        <v>156</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D16" s="12">
-        <v>657</v>
+        <v>598</v>
       </c>
       <c r="E16" s="12">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="F16" s="12">
-        <v>167</v>
+        <v>157</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1200,32 +1214,32 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B4" s="12">
-        <v>4346</v>
+        <v>4374</v>
       </c>
       <c r="C4" s="12">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D4" s="13">
         <v>115</v>
@@ -1233,35 +1247,35 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B5" s="12">
-        <v>1204</v>
+        <v>1207</v>
       </c>
       <c r="C5" s="12">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D5" s="13">
-        <v>1327</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B6" s="12">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="C6" s="12">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D6" s="13">
-        <v>98</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -1283,153 +1297,153 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C4" s="12">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="D4" s="12">
         <v>0</v>
       </c>
       <c r="E4" s="12">
-        <v>851</v>
+        <v>926</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C5" s="12">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="D5" s="12">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E5" s="12">
-        <v>2493</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C6" s="12">
-        <v>216</v>
+        <v>304</v>
       </c>
       <c r="D6" s="12">
         <v>1</v>
       </c>
       <c r="E6" s="12">
-        <v>1548</v>
+        <v>2212</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C7" s="12">
-        <v>127</v>
+        <v>61</v>
       </c>
       <c r="D7" s="12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E7" s="12">
-        <v>742</v>
+        <v>370</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C8" s="12">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D8" s="12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E8" s="12">
-        <v>559</v>
+        <v>545</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C9" s="12">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D9" s="12">
         <v>1</v>
       </c>
       <c r="E9" s="12">
-        <v>413</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C10" s="12">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D10" s="12">
         <v>1</v>
       </c>
       <c r="E10" s="12">
-        <v>726</v>
+        <v>701</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -1448,87 +1462,87 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
